--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -863,7 +863,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Витамины для щенков и растущих собак 100 таблеток</t>
+          <t>Витамины для щенков и растущих собак 8in1 Excel Multi Vit Puppy 100 шт</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Витамины для собак Glucosamine для суставов 55 таблеток</t>
+          <t>Витамины для собак для суставов 8in1 Excel Glucosamine 55 шт</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Витамины для взрослых собак для шерсти 70 таблеток</t>
+          <t>Витамины для взрослых собак 8in1 Excel Multi Vit Adult 70 шт</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Витамины для собак мелких пород 70 таблеток</t>
+          <t>Витамины для собак мелких пород Excel Multi Vitamin Small Breed 70 шт</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Витамины для пожилых собак от 5 лет 70 таблеток</t>
+          <t>Витамины для пожилых собак от 5 лет 8in1 Excel Multi Vitamin Senior 70 шт</t>
         </is>
       </c>
       <c r="C34" t="n">

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
+          <t>Беларусь, Минская область, Королёв Стан</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, Минская область, Королёв Стан</t>
+          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111734091-1-2.xlsx
+++ b/supplies/111734091-1-2.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
